--- a/src_files/data_files/fueldata_maf2020.xlsx
+++ b/src_files/data_files/fueldata_maf2020.xlsx
@@ -1,22 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\backbone\north_european_model (2IMatch)\src_files\data_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29C4684F-2065-4F30-8AE6-5E56F003E78D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88997609-D26C-4BF5-93BC-AD17D06A16C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20544" yWindow="0" windowWidth="20832" windowHeight="16656" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-75" windowWidth="29040" windowHeight="17520" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="fueldata" sheetId="1" r:id="rId1"/>
     <sheet name="data_fuelEmissions" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">fueldata!$A$1:$E$43</definedName>
     <definedName name="Bottom">OFFSET(#REF!,1,0,COUNT(#REF!),1)</definedName>
     <definedName name="Labels">OFFSET(Bottom,0,-1)</definedName>
   </definedNames>
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="21">
   <si>
     <t>Scenario</t>
   </si>
@@ -104,9 +105,6 @@
   </si>
   <si>
     <t>tCO2/MWh</t>
-  </si>
-  <si>
-    <t>H2 balanced</t>
   </si>
 </sst>
 </file>
@@ -305,16 +303,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E53"/>
-  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:F53"/>
+  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="19" customWidth="1"/>
-    <col min="3" max="3" width="22.6640625" customWidth="1"/>
-    <col min="4" max="4" width="11.5546875" style="7"/>
-    <col min="5" max="5" width="15.6640625" style="7" customWidth="1"/>
+    <col min="3" max="3" width="22.7109375" customWidth="1"/>
+    <col min="4" max="4" width="11.5703125" style="7"/>
+    <col min="5" max="5" width="15.7109375" style="7" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" ht="15" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -331,7 +329,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" ht="17.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
@@ -349,7 +347,7 @@
         <v>0.34200000000000003</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>3</v>
       </c>
@@ -367,7 +365,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>3</v>
       </c>
@@ -385,7 +383,7 @@
         <v>0.19800000000000001</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>3</v>
       </c>
@@ -403,7 +401,7 @@
         <v>0.28079999999999999</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>3</v>
       </c>
@@ -421,7 +419,7 @@
         <v>0.25559999999999999</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>3</v>
       </c>
@@ -439,7 +437,7 @@
         <v>0.37080000000000002</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>3</v>
       </c>
@@ -457,7 +455,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>3</v>
       </c>
@@ -475,7 +473,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>3</v>
       </c>
@@ -493,7 +491,7 @@
         <v>0.14399999999999999</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>3</v>
       </c>
@@ -511,7 +509,7 @@
         <v>0.41399999999999998</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
         <v>10</v>
       </c>
@@ -529,7 +527,7 @@
         <v>0.34200000000000003</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
         <v>10</v>
       </c>
@@ -547,7 +545,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
         <v>10</v>
       </c>
@@ -565,7 +563,7 @@
         <v>0.19800000000000001</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
         <v>10</v>
       </c>
@@ -583,7 +581,7 @@
         <v>0.28079999999999999</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
         <v>10</v>
       </c>
@@ -601,7 +599,7 @@
         <v>0.25559999999999999</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
         <v>10</v>
       </c>
@@ -619,7 +617,7 @@
         <v>0.37080000000000002</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
         <v>10</v>
       </c>
@@ -637,7 +635,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
         <v>10</v>
       </c>
@@ -655,7 +653,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A20" s="3" t="s">
         <v>10</v>
       </c>
@@ -673,7 +671,7 @@
         <v>0.14399999999999999</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
         <v>10</v>
       </c>
@@ -691,7 +689,7 @@
         <v>0.41399999999999998</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
         <v>10</v>
       </c>
@@ -709,7 +707,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
         <v>10</v>
       </c>
@@ -726,8 +724,9 @@
         <f>IFERROR(VLOOKUP($C23, data_fuelEmissions!$D$4:$F$14,3,FALSE), 0)</f>
         <v>0.34200000000000003</v>
       </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F23" s="6"/>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A24" s="3" t="s">
         <v>10</v>
       </c>
@@ -744,8 +743,9 @@
         <f>IFERROR(VLOOKUP($C24, data_fuelEmissions!$D$4:$F$14,3,FALSE), 0)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F24" s="6"/>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
         <v>10</v>
       </c>
@@ -762,8 +762,9 @@
         <f>IFERROR(VLOOKUP($C25, data_fuelEmissions!$D$4:$F$14,3,FALSE), 0)</f>
         <v>0.19800000000000001</v>
       </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F25" s="6"/>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A26" s="3" t="s">
         <v>10</v>
       </c>
@@ -780,8 +781,9 @@
         <f>IFERROR(VLOOKUP($C26, data_fuelEmissions!$D$4:$F$14,3,FALSE), 0)</f>
         <v>0.28079999999999999</v>
       </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F26" s="6"/>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A27" s="3" t="s">
         <v>10</v>
       </c>
@@ -798,8 +800,9 @@
         <f>IFERROR(VLOOKUP($C27, data_fuelEmissions!$D$4:$F$14,3,FALSE), 0)</f>
         <v>0.25559999999999999</v>
       </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F27" s="6"/>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A28" s="3" t="s">
         <v>10</v>
       </c>
@@ -816,8 +819,9 @@
         <f>IFERROR(VLOOKUP($C28, data_fuelEmissions!$D$4:$F$14,3,FALSE), 0)</f>
         <v>0.37080000000000002</v>
       </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F28" s="6"/>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A29" s="3" t="s">
         <v>10</v>
       </c>
@@ -834,8 +838,9 @@
         <f>IFERROR(VLOOKUP($C29, data_fuelEmissions!$D$4:$F$14,3,FALSE), 0)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F29" s="6"/>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A30" s="3" t="s">
         <v>10</v>
       </c>
@@ -852,8 +857,9 @@
         <f>IFERROR(VLOOKUP($C30, data_fuelEmissions!$D$4:$F$14,3,FALSE), 0)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F30" s="6"/>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A31" s="3" t="s">
         <v>10</v>
       </c>
@@ -870,8 +876,9 @@
         <f>IFERROR(VLOOKUP($C31, data_fuelEmissions!$D$4:$F$14,3,FALSE), 0)</f>
         <v>0.14399999999999999</v>
       </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F31" s="6"/>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A32" s="3" t="s">
         <v>10</v>
       </c>
@@ -888,8 +895,9 @@
         <f>IFERROR(VLOOKUP($C32, data_fuelEmissions!$D$4:$F$14,3,FALSE), 0)</f>
         <v>0.41399999999999998</v>
       </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F32" s="6"/>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A33" s="3" t="s">
         <v>10</v>
       </c>
@@ -906,8 +914,9 @@
         <f>IFERROR(VLOOKUP($C33, data_fuelEmissions!$D$4:$F$14,3,FALSE), 0)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F33" s="7"/>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A34" s="4" t="s">
         <v>11</v>
       </c>
@@ -925,7 +934,7 @@
         <v>0.34200000000000003</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A35" s="4" t="s">
         <v>11</v>
       </c>
@@ -943,7 +952,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A36" s="4" t="s">
         <v>11</v>
       </c>
@@ -961,7 +970,7 @@
         <v>0.19800000000000001</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A37" s="4" t="s">
         <v>11</v>
       </c>
@@ -979,7 +988,7 @@
         <v>0.28079999999999999</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A38" s="4" t="s">
         <v>11</v>
       </c>
@@ -997,7 +1006,7 @@
         <v>0.25559999999999999</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A39" s="4" t="s">
         <v>11</v>
       </c>
@@ -1015,7 +1024,7 @@
         <v>0.37080000000000002</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A40" s="4" t="s">
         <v>11</v>
       </c>
@@ -1033,7 +1042,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A41" s="4" t="s">
         <v>11</v>
       </c>
@@ -1051,7 +1060,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A42" s="4" t="s">
         <v>11</v>
       </c>
@@ -1062,14 +1071,14 @@
         <v>8</v>
       </c>
       <c r="D42" s="7">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E42" s="7">
         <f>IFERROR(VLOOKUP($C42, data_fuelEmissions!$D$4:$F$14,3,FALSE), 0)</f>
         <v>0.14399999999999999</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A43" s="4" t="s">
         <v>11</v>
       </c>
@@ -1080,194 +1089,55 @@
         <v>16</v>
       </c>
       <c r="D43" s="7">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E43" s="7">
         <f>IFERROR(VLOOKUP($C43, data_fuelEmissions!$D$4:$F$14,3,FALSE), 0)</f>
         <v>0.41399999999999998</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A44" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B44">
-        <v>2035</v>
-      </c>
-      <c r="C44" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D44" s="7">
-        <v>27</v>
-      </c>
-      <c r="E44" s="7">
-        <f>IFERROR(VLOOKUP($C44, data_fuelEmissions!$D$4:$F$14,3,FALSE), 0)</f>
-        <v>0.34200000000000003</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A45" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B45">
-        <v>2035</v>
-      </c>
-      <c r="C45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="D45" s="7">
-        <v>2.5</v>
-      </c>
-      <c r="E45" s="7">
-        <f>IFERROR(VLOOKUP($C45, data_fuelEmissions!$D$4:$F$14,3,FALSE), 0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A46" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B46">
-        <v>2035</v>
-      </c>
-      <c r="C46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D46" s="7">
-        <v>55</v>
-      </c>
-      <c r="E46" s="7">
-        <f>IFERROR(VLOOKUP($C46, data_fuelEmissions!$D$4:$F$14,3,FALSE), 0)</f>
-        <v>0.19800000000000001</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A47" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B47">
-        <v>2035</v>
-      </c>
-      <c r="C47" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D47" s="7">
-        <v>46</v>
-      </c>
-      <c r="E47" s="7">
-        <f>IFERROR(VLOOKUP($C47, data_fuelEmissions!$D$4:$F$14,3,FALSE), 0)</f>
-        <v>0.28079999999999999</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A48" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B48">
-        <v>2035</v>
-      </c>
-      <c r="C48" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D48" s="7">
-        <v>65</v>
-      </c>
-      <c r="E48" s="7">
-        <f>IFERROR(VLOOKUP($C48, data_fuelEmissions!$D$4:$F$14,3,FALSE), 0)</f>
-        <v>0.25559999999999999</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A49" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B49">
-        <v>2035</v>
-      </c>
-      <c r="C49" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D49" s="8">
-        <v>8</v>
-      </c>
-      <c r="E49" s="7">
-        <f>IFERROR(VLOOKUP($C49, data_fuelEmissions!$D$4:$F$14,3,FALSE), 0)</f>
-        <v>0.37080000000000002</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A50" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B50">
-        <v>2035</v>
-      </c>
-      <c r="C50" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D50" s="7">
-        <v>26</v>
-      </c>
-      <c r="E50" s="7">
-        <f>IFERROR(VLOOKUP($C50, data_fuelEmissions!$D$4:$F$14,3,FALSE), 0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A51" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B51">
-        <v>2035</v>
-      </c>
-      <c r="C51" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D51" s="7">
-        <v>1</v>
-      </c>
-      <c r="E51" s="7">
-        <f>IFERROR(VLOOKUP($C51, data_fuelEmissions!$D$4:$F$14,3,FALSE), 0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A52" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B52">
-        <v>2035</v>
-      </c>
-      <c r="C52" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D52" s="7">
-        <v>10</v>
-      </c>
-      <c r="E52" s="7">
-        <f>IFERROR(VLOOKUP($C52, data_fuelEmissions!$D$4:$F$14,3,FALSE), 0)</f>
-        <v>0.14399999999999999</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A53" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B53">
-        <v>2035</v>
-      </c>
-      <c r="C53" t="s">
-        <v>16</v>
-      </c>
-      <c r="D53" s="7">
-        <v>0</v>
-      </c>
-      <c r="E53" s="7">
-        <f>IFERROR(VLOOKUP($C53, data_fuelEmissions!$D$4:$F$14,3,FALSE), 0)</f>
-        <v>0.41399999999999998</v>
-      </c>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A44" s="4"/>
+      <c r="C44" s="3"/>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A45" s="4"/>
+      <c r="C45" s="3"/>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A46" s="4"/>
+      <c r="C46" s="3"/>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A47" s="4"/>
+      <c r="C47" s="3"/>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A48" s="4"/>
+      <c r="C48" s="3"/>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A49" s="4"/>
+      <c r="C49" s="3"/>
+      <c r="D49" s="8"/>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A50" s="4"/>
+      <c r="C50" s="3"/>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A51" s="4"/>
+      <c r="C51" s="3"/>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A52" s="4"/>
+      <c r="C52" s="3"/>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A53" s="4"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:E43" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter>
@@ -1280,12 +1150,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29F8F8B4-D0EB-4745-A354-04E35BFEA174}">
   <dimension ref="D4:F14"/>
-  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="4" max="4" width="12.33203125" customWidth="1"/>
+    <col min="4" max="4" width="12.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="4:6" x14ac:dyDescent="0.2">
       <c r="E4" t="s">
         <v>19</v>
       </c>
@@ -1293,7 +1163,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="4:6" x14ac:dyDescent="0.2">
       <c r="D5" t="s">
         <v>13</v>
       </c>
@@ -1305,7 +1175,7 @@
         <v>0.34200000000000003</v>
       </c>
     </row>
-    <row r="6" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="4:6" x14ac:dyDescent="0.2">
       <c r="D6" t="s">
         <v>4</v>
       </c>
@@ -1314,7 +1184,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="4:6" x14ac:dyDescent="0.2">
       <c r="D7" t="s">
         <v>5</v>
       </c>
@@ -1326,7 +1196,7 @@
         <v>0.19800000000000001</v>
       </c>
     </row>
-    <row r="8" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="4:6" x14ac:dyDescent="0.2">
       <c r="D8" t="s">
         <v>15</v>
       </c>
@@ -1338,7 +1208,7 @@
         <v>0.28079999999999999</v>
       </c>
     </row>
-    <row r="9" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="4:6" x14ac:dyDescent="0.2">
       <c r="D9" t="s">
         <v>14</v>
       </c>
@@ -1350,7 +1220,7 @@
         <v>0.25559999999999999</v>
       </c>
     </row>
-    <row r="10" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="4:6" x14ac:dyDescent="0.2">
       <c r="D10" t="s">
         <v>6</v>
       </c>
@@ -1362,7 +1232,7 @@
         <v>0.37080000000000002</v>
       </c>
     </row>
-    <row r="11" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="4:6" x14ac:dyDescent="0.2">
       <c r="D11" t="s">
         <v>7</v>
       </c>
@@ -1374,7 +1244,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="4:6" x14ac:dyDescent="0.2">
       <c r="D12" t="s">
         <v>17</v>
       </c>
@@ -1386,7 +1256,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="4:6" x14ac:dyDescent="0.2">
       <c r="D13" t="s">
         <v>8</v>
       </c>
@@ -1398,7 +1268,7 @@
         <v>0.14399999999999999</v>
       </c>
     </row>
-    <row r="14" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="4:6" x14ac:dyDescent="0.2">
       <c r="D14" t="s">
         <v>16</v>
       </c>
